--- a/AAII_Financials/Quarterly/SSEZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSEZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="92">
   <si>
     <t>SSEZY</t>
   </si>
@@ -656,90 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -776,23 +783,29 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>4649800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3695700</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -829,23 +842,29 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>1556100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2205500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -882,23 +901,29 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
         <v>3093600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1490100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,8 +943,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -971,8 +998,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1057,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1062,23 +1101,29 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-207200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-429100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1115,11 +1160,11 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1130,8 +1175,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,8 +1199,10 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1186,23 +1239,29 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3">
         <v>2150800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2462300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1239,23 +1298,29 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>2499000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1233300</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,8 +1340,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1313,23 +1380,29 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-42600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>35600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1366,23 +1439,29 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>2698800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1628800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1419,23 +1498,29 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
         <v>243800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>246200</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1472,23 +1557,29 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3">
         <v>2212500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1022700</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1525,23 +1616,29 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>711600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>104100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,8 +1690,14 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1631,23 +1734,29 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1500900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>918700</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1684,23 +1793,29 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1434400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>857500</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1867,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1790,23 +1911,29 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-123100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>60400</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1985,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,8 +2044,14 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1949,23 +2088,29 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>42600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2002,23 +2147,29 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1311300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>917900</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,8 +2221,14 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2108,81 +2265,93 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1311300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>917900</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2371,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,61 +2394,69 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2037400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2076600</v>
+      </c>
+      <c r="F41" s="3">
         <v>582400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>593600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1408900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1365200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1193900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1125800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1308300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1319500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1101200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1146800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1103300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>545200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,379 +2508,427 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2751500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2804400</v>
+      </c>
+      <c r="F43" s="3">
         <v>3713900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3785300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2696700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2613000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3609400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3403400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2635700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2658200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2951500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3073500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2865200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1975600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>573300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>584400</v>
+      </c>
+      <c r="F44" s="3">
         <v>388700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>396200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>598100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>579500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>444000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>418700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>433200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>436900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>300200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>312600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>488500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>216600</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1617600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1648700</v>
+      </c>
+      <c r="F45" s="3">
         <v>511200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>521000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>737900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>715000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>999300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>942300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1630300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1644200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>642500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>669100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1931700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1596300</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8253700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8412700</v>
+      </c>
+      <c r="F46" s="3">
         <v>5196300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5296200</v>
       </c>
-      <c r="F46" s="3">
-        <v>6585900</v>
-      </c>
-      <c r="G46" s="3">
-        <v>6381600</v>
-      </c>
       <c r="H46" s="3">
+        <v>6265700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>6071300</v>
+      </c>
+      <c r="J46" s="3">
         <v>6246700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5890200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6768200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6825900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4995400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5202000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7133100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4333800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2578500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2628100</v>
+      </c>
+      <c r="F47" s="3">
         <v>2527500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2576100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2579000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2499000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2543100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2397900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2483500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2504700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2449200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2550500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2478100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3198000</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29079800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>29639700</v>
+      </c>
+      <c r="F48" s="3">
         <v>27151800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>27674100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>24320900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>23566400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>23403200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>22067200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>20979900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>21159000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>19508900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>20315900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>19046800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>17180500</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1750400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1784100</v>
+      </c>
+      <c r="F49" s="3">
         <v>3012100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3070000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1719800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1666400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3165900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2985200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1901300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1917500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2589600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2696800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1776800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1067700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2980,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,61 +3039,73 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1354400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1380500</v>
+      </c>
+      <c r="F52" s="3">
         <v>1517500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1546700</v>
       </c>
-      <c r="F52" s="3">
-        <v>738600</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>1050500</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1017900</v>
+      </c>
+      <c r="J52" s="3">
         <v>715700</v>
       </c>
-      <c r="H52" s="3">
-        <v>715700</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>674900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>613600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>618800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>663100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>690500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>973700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>924800</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,61 +3157,73 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>46683400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>47582200</v>
+      </c>
+      <c r="F54" s="3">
         <v>41467600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>42265200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>39230000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>38012900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>38307600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>36120800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>35704600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>36009300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>31861300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>33179300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>33621700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>26704800</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3243,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,326 +3266,364 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1186700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1209600</v>
+      </c>
+      <c r="F57" s="3">
         <v>3089800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3149200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>918200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>889700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3794400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3577800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>829400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>836500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3106300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3234800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>859300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2003700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1590400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1621000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2114800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2155500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2605800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2525000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2551800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2406100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1464200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1476700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1702200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1772600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2269000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1789200</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2049100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2088600</v>
+      </c>
+      <c r="F59" s="3">
         <v>176800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>180200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1035900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1003800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>456900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>430800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1653700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1667900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>700500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>729400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2057400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1033100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6886500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7019100</v>
+      </c>
+      <c r="F60" s="3">
         <v>5381300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5484900</v>
       </c>
-      <c r="F60" s="3">
-        <v>6551900</v>
-      </c>
-      <c r="G60" s="3">
-        <v>6348600</v>
-      </c>
       <c r="H60" s="3">
+        <v>6306800</v>
+      </c>
+      <c r="I60" s="3">
+        <v>6111100</v>
+      </c>
+      <c r="J60" s="3">
         <v>6803100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6414800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6139100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6191500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5509000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5736900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6857600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4826000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11839400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>12067300</v>
+      </c>
+      <c r="F61" s="3">
         <v>11956100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>12186100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11234400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10885900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>10287800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>9700500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10192500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10279500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9223300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>9604800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9053800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>11405100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1282000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1306700</v>
+      </c>
+      <c r="F62" s="3">
         <v>3190600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3252000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1049100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1016600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1252800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1181300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1144900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1154700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2402100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2501400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1204200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3657500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3675,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3734,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,61 +3793,73 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25026000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>25507800</v>
+      </c>
+      <c r="F66" s="3">
         <v>23161000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>23606500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>22830800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>22122500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>22129300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>20866100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>20797600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>20975100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>18785300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>19562300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>19910300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>19888600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3879,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3934,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3993,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +4052,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,61 +4111,73 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11750500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>11976700</v>
+      </c>
+      <c r="F72" s="3">
         <v>10963200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>11174100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>10771100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>10436900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>10211400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>9628400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>9522800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>9604100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>7493700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>7803700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>8236300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3215000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4229,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4288,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,61 +4347,73 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20665000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>21062900</v>
+      </c>
+      <c r="F76" s="3">
         <v>17371800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>17706000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15586800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>15103200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>15131100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14267300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14206200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>14327500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>12217700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12723100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>12908400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6816200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,66 +4465,78 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4184,23 +4573,29 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1311300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>917900</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,61 +4615,69 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>191800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>185800</v>
+      </c>
+      <c r="F83" s="3">
         <v>247100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>233000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>219900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>221800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>171100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>178200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>167900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>163600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>186200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>203100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>117200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>242500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4729,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4788,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4847,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4906,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4965,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1400200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1427200</v>
+      </c>
+      <c r="F89" s="3">
         <v>883400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>900400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>905600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>877500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>720400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>679300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1156300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1166100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1238000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1289200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>607900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>903100</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,50 +5051,52 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1442700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1470500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1318600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1344000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1002700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-971600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-762000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-718500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-708700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-714800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-517400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-538800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-531700</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -4665,8 +5106,14 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +5165,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,61 +5224,73 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1613800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1644900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1465000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1493200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1180300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1143700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-999400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-942300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-1057200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1066200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-722500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-752400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-750900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1216800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,61 +5310,69 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>101300</v>
+      </c>
+      <c r="F96" s="3">
         <v>351800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>358500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>122900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>119100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>191300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>180400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>132300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>133400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>476800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>496500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>95400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-345100</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5424,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5483,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,61 +5542,73 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>946200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>964400</v>
+      </c>
+      <c r="F100" s="3">
         <v>139900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>142600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>403800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>391200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>181700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>171400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-14800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-14900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-509000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-530000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>515800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1480700</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5148,11 +5645,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5163,57 +5660,69 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>732600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>746700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-441700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-450200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>129000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>125000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-97200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-91700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>84300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>85000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>6500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>6700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>372700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1794400</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
